--- a/education_forms/005_paraphrasing_quotation_use_guide--education_forms.xlsx
+++ b/education_forms/005_paraphrasing_quotation_use_guide--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,69 +515,69 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input</t>
+          <t>purpose_of_paraphrasing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paraphrasing &amp; Quotation Use Guide Form</t>
+          <t>What is the purpose of paraphrasing and quotation use in communication?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>section_1</t>
+          <t>common_mistakes_paraphrasing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Section 1</t>
+          <t>What are some common mistakes to avoid when paraphrasing and quoting others' words?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>section_2</t>
+          <t>determine_paraphrase_or_quote</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Section 2</t>
+          <t>How do you determine when to paraphrase or quote someone's words?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>section_3</t>
+          <t>effective_paraphrasing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Section 3</t>
+          <t>What are some strategies for effectively paraphrasing and quoting in different contexts?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>section_3_1</t>
+          <t>handle_disagreements</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Section 3</t>
+          <t>How do you handle disagreements or misunderstandings that arise from paraphrasing and quoting?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>section_4</t>
+          <t>example_paraphrased_sentence</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Section 4</t>
+          <t>Can you provide an example of a well-crafted paraphrased sentence?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>section_4_1</t>
+          <t>example_quoted_sentence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Section 4</t>
+          <t>Can you provide an example of a well-crafted quoted sentence?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,64 +681,64 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>section_5</t>
+          <t>quote_in_academic_writing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Section 5</t>
+          <t>What are some best practices for using quotes in academic writing?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>section_6</t>
+          <t>effective_paraphrasing_situation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Section 6</t>
+          <t>Can you describe a situation where paraphrasing was effective in communication?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>section_7</t>
+          <t>effective_quoting_situation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Section 7</t>
+          <t>Can you describe a situation where quoting was effective in communication?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,58 +750,58 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>section_7_1</t>
+          <t>unclear_original_meaning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Section 7</t>
+          <t>How do you handle situations where the original speaker's meaning is unclear or ambiguous?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>section_8</t>
+          <t>avoid_unintentional_plagiarism</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Section 8</t>
+          <t>What are some tips for avoiding unintentional plagiarism when paraphrasing and quoting?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>section_8_1</t>
+          <t>section_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Section 8</t>
+          <t>Section 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>section_9</t>
+          <t>section_13_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Section 9</t>
+          <t>Section 13 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>section_9_1</t>
+          <t>section_14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Section 9</t>
+          <t>Section 14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>section_10</t>
+          <t>section_14_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Section 10</t>
+          <t>Section 14 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>section_10_1</t>
+          <t>section_15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Section 10</t>
+          <t>Section 15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>section_11</t>
+          <t>section_15_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Section 11</t>
+          <t>Section 15 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>section_11_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Section 11</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>section_12</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Section 12</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>section_12_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Section 12</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>section_13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Section 13</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>section_13_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Section 13</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>section_14</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Section 14</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>section_14_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Section 14</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,306 +965,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>common_mistakes_paraphrasing_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>inaccurate_representation_of_the_original_text</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Inaccurate representation of the original text</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>common_mistakes_paraphrasing_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>lack_of_context</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Lack of context</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>common_mistakes_paraphrasing_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>failure_to_properly_cite_sources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Failure to properly cite sources</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>common_mistakes_paraphrasing_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>overuse_of_quotes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Overuse of quotes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>common_mistakes_paraphrasing_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>underuse_of_paraphrasing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Underuse of paraphrasing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>determine_paraphrase_or_quote_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>always_paraphrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Always paraphrase</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>section_6_choices</t>
+          <t>determine_paraphrase_or_quote_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>always_quote</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Always quote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>section_6_choices</t>
+          <t>determine_paraphrase_or_quote_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>it_depends_on_the_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>It depends on the context</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>section_6_choices</t>
+          <t>determine_paraphrase_or_quote_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>section_7_choices</t>
+          <t>section_13_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>section_7_choices</t>
+          <t>section_13_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>section_7_choices</t>
+          <t>section_13_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>section_12_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>section_12_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>section_12_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>section_13_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>section_13_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>section_13_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
